--- a/ig/DM_FINESS_New/ValueSet-jdv-j371-etat-objet-administratif-finess.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j371-etat-objet-administratif-finess.xlsx
@@ -111,7 +111,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r365-etat-objet</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r365-etat-objet-structure</t>
   </si>
 </sst>
 </file>

--- a/ig/DM_FINESS_New/ValueSet-jdv-j371-etat-objet-administratif-finess.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j371-etat-objet-administratif-finess.xlsx
@@ -111,7 +111,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r365-etat-objet-structure</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r365-etat-objet</t>
   </si>
 </sst>
 </file>
